--- a/Shablon/TPS2024.xlsx
+++ b/Shablon/TPS2024.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <r>
       <t>τ</t>
@@ -667,13 +667,6 @@
   </si>
   <si>
     <t>dcv4_6</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"
-СГМетр, лаборатория средств электрических и радиотехнических измерений
-125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23
-Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014
-Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.ru</t>
   </si>
   <si>
     <t>Измеренное напряжение (кан. 1)</t>
@@ -1055,6 +1048,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1074,12 +1101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1105,34 +1126,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1474,32 +1467,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="9" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
     </row>
     <row r="2" spans="1:10" s="9" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="59" t="str">
+      <c r="A3" s="43" t="str">
         <f>"Протокол поверки № 10/"&amp;C53&amp;"/"&amp;D6</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
       <c r="J3" s="41"/>
     </row>
     <row r="4" spans="1:10" s="9" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1513,11 +1504,11 @@
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="20" t="s">
         <v>53</v>
       </c>
@@ -1530,11 +1521,11 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="38" t="s">
         <v>56</v>
       </c>
@@ -1545,11 +1536,11 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="20"/>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -1558,11 +1549,11 @@
       <c r="I7" s="32"/>
     </row>
     <row r="8" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="23" t="s">
         <v>64</v>
       </c>
@@ -1573,11 +1564,11 @@
       <c r="I8" s="32"/>
     </row>
     <row r="9" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="38" t="s">
         <v>60</v>
       </c>
@@ -1588,37 +1579,37 @@
       <c r="I9" s="32"/>
     </row>
     <row r="10" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="52" t="s">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="63"/>
       <c r="I10" s="33"/>
     </row>
     <row r="11" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="57"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="66"/>
       <c r="I11" s="33"/>
     </row>
     <row r="12" spans="1:10" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="34" t="s">
         <v>63</v>
       </c>
@@ -1660,68 +1651,68 @@
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:9" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="44" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="65" t="s">
+      <c r="F17" s="56"/>
+      <c r="G17" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="65"/>
+      <c r="H17" s="50"/>
     </row>
     <row r="18" spans="1:9" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="46" t="s">
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="46"/>
-      <c r="G18" s="51" t="s">
+      <c r="F18" s="57"/>
+      <c r="G18" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="51"/>
+      <c r="H18" s="53"/>
     </row>
     <row r="19" spans="1:9" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="46" t="s">
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="46"/>
-      <c r="G19" s="51" t="s">
+      <c r="F19" s="57"/>
+      <c r="G19" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="51"/>
+      <c r="H19" s="53"/>
     </row>
     <row r="20" spans="1:9" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="46" t="s">
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="51" t="s">
+      <c r="F20" s="57"/>
+      <c r="G20" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="51"/>
+      <c r="H20" s="53"/>
     </row>
     <row r="21" spans="1:9" s="9" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
@@ -1732,17 +1723,17 @@
       <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:9" s="9" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
     </row>
     <row r="23" spans="1:9" s="9" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
@@ -1825,16 +1816,16 @@
         <v>22</v>
       </c>
       <c r="C32" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="E32" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="F32" s="18" t="s">
         <v>109</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>110</v>
       </c>
       <c r="G32" s="18" t="s">
         <v>23</v>
@@ -1980,14 +1971,14 @@
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
@@ -2034,7 +2025,7 @@
         <v>85</v>
       </c>
       <c r="F43" s="42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -2046,17 +2037,17 @@
       <c r="F44" s="8"/>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="64" t="s">
+      <c r="A45" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="64"/>
-      <c r="C45" s="64"/>
-      <c r="D45" s="64"/>
-      <c r="E45" s="64"/>
-      <c r="F45" s="64"/>
-      <c r="G45" s="64"/>
-      <c r="H45" s="64"/>
-      <c r="I45" s="64"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
     </row>
     <row r="46" spans="1:9" s="1" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
@@ -2134,10 +2125,10 @@
       <c r="E50" s="15"/>
     </row>
     <row r="51" spans="1:9" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="60" t="s">
+      <c r="A51" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="60"/>
+      <c r="B51" s="44"/>
       <c r="C51" s="25"/>
       <c r="D51" s="26"/>
       <c r="E51" s="27"/>
@@ -2146,32 +2137,32 @@
       <c r="H51" s="1"/>
     </row>
     <row r="52" spans="1:9" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="60"/>
+      <c r="B52" s="44"/>
       <c r="C52" s="26"/>
       <c r="D52" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E52" s="61" t="s">
+      <c r="E52" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="62"/>
+      <c r="F52" s="46"/>
       <c r="G52" s="27" t="s">
         <v>80</v>
       </c>
       <c r="H52" s="31"/>
     </row>
     <row r="53" spans="1:9" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="63" t="s">
+      <c r="B53" s="44"/>
+      <c r="C53" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D53" s="63"/>
+      <c r="D53" s="47"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2292,20 +2283,6 @@
     <row r="166" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
@@ -2322,6 +2299,20 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.19685039370078741" top="0.39370078740157483" bottom="0.75181159420289856" header="0.51181102362204722" footer="0.51181102362204722"/>
